--- a/artfynd/A 74502-2021 artfynd.xlsx
+++ b/artfynd/A 74502-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 74502-2021 artfynd.xlsx
+++ b/artfynd/A 74502-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117101481</v>
+        <v>117101463</v>
       </c>
       <c r="B6" t="n">
-        <v>57297</v>
+        <v>57521</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1276,126 +1276,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>117101463</v>
-      </c>
-      <c r="B7" t="n">
-        <v>57521</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>103012</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Grönsångare</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Phylloscopus sibilatrix</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Prästdammarna, Össjö vindpark, Sk</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>382414</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6234392</v>
-      </c>
-      <c r="S7" t="n">
-        <v>50</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Ängelholm</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Össjö</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2024-05-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-05-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Henrik Johansson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Henrik Johansson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 74502-2021 artfynd.xlsx
+++ b/artfynd/A 74502-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103466380</v>
+        <v>103958889</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2023</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Schrad.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Prästdammarna, Össjö vindpark, Sk</t>
+          <t>Enskiftet, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>382414.4430632774</v>
+        <v>382431</v>
       </c>
       <c r="R2" t="n">
-        <v>6234391.914170312</v>
+        <v>6234258</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,73 +760,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Johansson</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henrik Johansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103466403</v>
+        <v>103958884</v>
       </c>
       <c r="B3" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Prästdammarna, Össjö vindpark, Sk</t>
+          <t>Enskiftet, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>382414.4430632774</v>
+        <v>382348</v>
       </c>
       <c r="R3" t="n">
-        <v>6234391.914170312</v>
+        <v>6234331</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,27 +861,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henrik Johansson</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henrik Johansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>103958892</v>
       </c>
       <c r="B4" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>382519.4586932392</v>
+        <v>382519</v>
       </c>
       <c r="R4" t="n">
-        <v>6234321.199013441</v>
+        <v>6234321</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,19 +945,9 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117101507</v>
+        <v>117101499</v>
       </c>
       <c r="B5" t="n">
-        <v>56593</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,16 +1006,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1159,45 +1093,44 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117101463</v>
+        <v>103466380</v>
       </c>
       <c r="B6" t="n">
-        <v>57521</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1237,22 +1170,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,6 +1209,470 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102352464</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Prästdammarna, Össjö vindpark, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>382414</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6234392</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Össjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Henrik Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>117101463</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Prästdammarna, Össjö vindpark, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>382414</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6234392</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Össjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Henrik Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henrik Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>102352448</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Prästdammarna, Össjö vindpark, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>382414</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6234392</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Össjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Henrik Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henrik Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>103466403</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Prästdammarna, Össjö vindpark, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>382414</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6234392</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Össjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Henrik Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Henrik Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 74502-2021 artfynd.xlsx
+++ b/artfynd/A 74502-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103958889</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103958884</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103958892</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117101499</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103466380</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102352464</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1443,6 +1478,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117101463</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1558,6 +1598,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102352448</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,8 +1718,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103466403</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>